--- a/artfynd/S 651-2026 artfynd.xlsx
+++ b/artfynd/S 651-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY139"/>
+  <dimension ref="A1:AZ139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207967</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207980</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1060,6 +1075,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79519087</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1196,6 +1216,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79519088</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1332,6 +1357,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79519095</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1468,6 +1498,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79519096</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1604,6 +1639,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79519237</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1740,6 +1780,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79519238</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1876,6 +1921,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79519241</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2012,6 +2062,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79519242</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2138,6 +2193,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207862</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2264,6 +2324,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207865</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2390,6 +2455,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207870</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2516,6 +2586,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207872</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2642,6 +2717,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207875</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2768,6 +2848,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207877</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2894,6 +2979,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207915</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3020,6 +3110,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207921</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3146,6 +3241,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207972</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3272,6 +3372,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207975</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3398,6 +3503,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207984</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3524,6 +3634,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207985</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3650,6 +3765,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207994</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3776,6 +3896,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131208002</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3902,6 +4027,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131208011</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4038,6 +4168,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522447</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4164,6 +4299,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207977</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4290,6 +4430,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207987</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4426,6 +4571,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523436</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4552,6 +4702,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207868</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4678,6 +4833,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207879</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4804,6 +4964,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207904</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4930,6 +5095,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207912</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5056,6 +5226,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207934</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5182,6 +5357,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207991</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5308,6 +5488,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207992</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5434,6 +5619,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131208005</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5570,6 +5760,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520108</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5706,6 +5901,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520109</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5842,6 +6042,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520176</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5978,6 +6183,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520177</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6114,6 +6324,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520181</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6250,6 +6465,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520185</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6386,6 +6606,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520190</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6522,6 +6747,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79520191</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6648,6 +6878,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207878</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6774,6 +7009,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207918</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6900,6 +7140,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207935</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7026,6 +7271,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207947</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7152,6 +7402,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207983</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7278,6 +7533,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207996</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7404,6 +7664,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131208004</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7540,6 +7805,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522779</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7676,6 +7946,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79522780</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7802,6 +8077,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207988</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7929,6 +8209,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523584</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8056,6 +8341,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523585</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8183,6 +8473,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523592</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8310,6 +8605,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523593</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8437,6 +8737,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523594</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8564,6 +8869,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523595</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8691,6 +9001,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523596</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8818,6 +9133,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523597</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8954,6 +9274,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523205</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -9090,6 +9415,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523206</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -9226,6 +9556,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523302</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9362,6 +9697,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523303</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9498,6 +9838,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523304</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9624,6 +9969,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207867</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9750,6 +10100,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207920</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9876,6 +10231,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207946</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -10002,6 +10362,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207949</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -10128,6 +10493,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207966</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -10254,6 +10624,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207970</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -10380,6 +10755,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207974</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -10506,6 +10886,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207979</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10632,6 +11017,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207989</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10758,6 +11148,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207997</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10884,6 +11279,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131208003</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -11010,6 +11410,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207860</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -11136,6 +11541,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207861</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -11262,6 +11672,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207864</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -11388,6 +11803,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207869</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -11514,6 +11934,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207871</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -11640,6 +12065,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207876</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11766,6 +12196,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207902</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11892,6 +12327,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207905</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -12018,6 +12458,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207913</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -12144,6 +12589,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207917</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -12270,6 +12720,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207919</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -12396,6 +12851,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207922</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -12522,6 +12982,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207926</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -12648,6 +13113,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207928</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -12774,6 +13244,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207930</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -12900,6 +13375,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207932</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -13026,6 +13506,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207937</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -13152,6 +13637,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207938</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -13278,6 +13768,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207943</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -13404,6 +13899,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207965</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -13530,6 +14030,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207971</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -13656,6 +14161,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207973</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -13782,6 +14292,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207976</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -13908,6 +14423,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207981</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -14034,6 +14554,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207982</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -14160,6 +14685,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207986</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -14286,6 +14816,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207993</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -14412,6 +14947,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131208001</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -14538,6 +15078,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131208008</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -14674,6 +15219,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79519841</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -14800,6 +15350,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207863</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -14926,6 +15481,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207866</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -15052,6 +15612,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207944</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -15178,6 +15743,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207968</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -15304,6 +15874,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207999</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -15430,6 +16005,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131208006</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -15566,6 +16146,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523109</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -15702,6 +16287,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523110</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -15838,6 +16428,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79523113</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -15964,6 +16559,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207903</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -16090,6 +16690,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207906</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -16216,6 +16821,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207914</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -16342,6 +16952,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207916</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -16468,6 +17083,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207927</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -16594,6 +17214,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207929</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -16720,6 +17345,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207931</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -16846,6 +17476,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207933</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -16972,6 +17607,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207936</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -17098,6 +17738,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207939</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -17224,6 +17869,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131208000</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -17350,6 +18000,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207945</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -17476,6 +18131,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207948</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -17602,6 +18262,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207969</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -17728,6 +18393,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207978</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -17854,6 +18524,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207990</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -17980,6 +18655,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207995</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -18106,6 +18786,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131207998</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -18232,6 +18917,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131208007</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -18358,8 +19048,153 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131208010</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>